--- a/examples/hayden_case_studies/nebraska_k12_finance.xlsx
+++ b/examples/hayden_case_studies/nebraska_k12_finance.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -47,26 +47,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
         <bgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -103,9 +97,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -539,7 +530,7 @@
 money: Department of Education operational budget for administratio...</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>money: $800 million annual state aid appropriation distributed via ...
 rule: TEEOSA formula compliance requirements including cost groupi...</t>
@@ -556,7 +547,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr"/>
       <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>information: Academic performance standards, curriculum frameworks, asses...
 authority: Authority to conduct compliance audits, review instructional...</t>
@@ -587,13 +578,13 @@
           <t>Taxpayers</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>money: Property tax revenue collected at local and state levels to ...</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>money: Direct property tax levies for local school district operati...</t>
         </is>
@@ -634,145 +625,145 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Delivery Count</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Department of Education</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>School Districts</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Department of Education establishes academic standards and reporting requirements for school districts, including student performance benchmarks, teacher certification standards, and financial accountability measures.</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Taxpayers</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>School Districts</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Taxpayers directly fund school districts through local property tax levies, which supplement state aid and create funding disparities based on local wealth.</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Taxpayers</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>State Legislature</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Taxpayers provide property tax revenue that funds both state aid (via general fund) and local school district budgets. Nebraska relies heavily on property taxes for education funding, creating ongoing tension over tax equity.</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>School Districts</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>School districts provide K-12 educational services to students, including classroom instruction, special education, extracurricular activities, transportation, food services, and counseling.</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>State Legislature</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Department of Education</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Legislature grants Department of Education oversight authority over school districts, including power to audit financial records, review academic programs, and enforce state standards.</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>State Legislature</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>School Districts</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Legislature provides state aid to school districts through TEEOSA formula, which equalizes funding based on property valuations and student needs. Formula includes basic allowance, special education weighting, poverty adjustments, and transportation costs.</t>
         </is>
       </c>
-      <c r="D2" s="9" t="n">
+      <c r="D7" s="8" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>State Legislature</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Department of Education</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Legislature grants Department of Education oversight authority over school districts, including power to audit financial records, review academic programs, and enforce state standards.</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>School Districts</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>School districts provide comprehensive K-12 educational services to students, including classroom instruction, special education programs, extracurricular activities, transportation, food services, and counseling.</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Department of Education</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>School Districts</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Department of Education establishes academic standards and reporting requirements for school districts, including student performance benchmarks, teacher certification standards, and financial accountability measures.</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Taxpayers</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>State Legislature</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Taxpayers provide property tax revenue that funds both state aid (via general fund) and local school district budgets. Nebraska relies heavily on property taxes for education funding, creating ongoing tension over tax equity.</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Taxpayers</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>School Districts</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Taxpayers directly fund school districts through local property tax levies, which supplement state aid and create funding disparities based on local wealth.</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -848,318 +839,318 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Department of Education</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>School Districts</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>information</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Academic performance standards, curriculum frameworks, assessment requirements, and data reporting specifications</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n"/>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="H2" s="9" t="n"/>
+      <c r="I2" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Department of Education</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>School Districts</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>authority</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Authority to conduct compliance audits, review instructional programs, and approve/deny accreditation</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n"/>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>event-triggered</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="n"/>
+      <c r="I3" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Taxpayers</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>School Districts</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>money</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Direct property tax levies for local school district operations</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>800000000</v>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>USD/year</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="n"/>
+      <c r="I4" s="9" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Taxpayers</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>State Legislature</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>money</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Property tax revenue collected at local and state levels to fund education</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>1200000000</v>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>USD/year</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>1500000000</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>School Districts</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>energy</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>K-12 instructional services including core subjects, special education, extracurricular activities, counseling, and transportation</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="n"/>
+      <c r="I6" s="9" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>State Legislature</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Department of Education</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>authority</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Statutory authority to oversee school district compliance, conduct audits, and enforce academic standards</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="9" t="n"/>
+      <c r="I7" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>State Legislature</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Department of Education</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>money</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Department of Education operational budget for administration and oversight</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>USD/year</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="n"/>
+      <c r="I8" s="9" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>State Legislature</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>School Districts</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>money</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>$800 million annual state aid appropriation distributed via TEEOSA formula</t>
         </is>
       </c>
-      <c r="E2" s="10" t="n">
+      <c r="E9" s="9" t="n">
         <v>800000000</v>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>USD/year</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
-      <c r="H2" s="10" t="n"/>
-      <c r="I2" s="10" t="n">
+      <c r="H9" s="9" t="n"/>
+      <c r="I9" s="9" t="n">
         <v>0.95</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>State Legislature</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>School Districts</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>rule</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>TEEOSA formula compliance requirements including cost grouping, needs calculations, and local effort rate provisions</t>
         </is>
       </c>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="8" t="n"/>
-      <c r="G3" s="8" t="n"/>
-      <c r="H3" s="10" t="n"/>
-      <c r="I3" s="10" t="n">
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="9" t="n"/>
+      <c r="I10" s="9" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>State Legislature</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Department of Education</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>authority</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Statutory authority to oversee school district compliance, conduct audits, and enforce academic standards</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="8" t="n"/>
-      <c r="G4" s="8" t="n"/>
-      <c r="H4" s="10" t="n"/>
-      <c r="I4" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>State Legislature</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Department of Education</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Department of Education operational budget for administration and oversight</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>25000000</v>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>USD/year</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="n"/>
-      <c r="I5" s="10" t="n">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>School Districts</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>energy</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>K-12 instructional services including core subjects, special education, extracurricular activities, counseling, and transportation</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>continuous</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="10" t="n">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Department of Education</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>School Districts</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>information</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Academic performance standards, curriculum frameworks, assessment requirements, and data reporting specifications</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="n"/>
-      <c r="F7" s="8" t="n"/>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>continuous</t>
-        </is>
-      </c>
-      <c r="H7" s="10" t="n"/>
-      <c r="I7" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Department of Education</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>School Districts</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>authority</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Authority to conduct compliance audits, review instructional programs, and approve/deny accreditation</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>event-triggered</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="n"/>
-      <c r="I8" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Taxpayers</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>State Legislature</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Property tax revenue collected at local and state levels to fund education</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>1200000000</v>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>USD/year</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>1500000000</v>
-      </c>
-      <c r="I9" s="10" t="n">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Taxpayers</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>School Districts</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Direct property tax levies for local school district operations</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>800000000</v>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>USD/year</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="n"/>
-      <c r="I10" s="10" t="n">
-        <v>0.95</v>
       </c>
     </row>
   </sheetData>

--- a/examples/hayden_case_studies/nebraska_k12_finance.xlsx
+++ b/examples/hayden_case_studies/nebraska_k12_finance.xlsx
@@ -649,17 +649,17 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
+          <t>State Legislature</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>School Districts</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Department of Education establishes academic standards and reporting requirements for school districts, including student performance benchmarks, teacher certification standards, and financial accountability measures.</t>
+          <t>Legislature grants Department of Education oversight authority over school districts, including power to audit financial records, review academic programs, and enforce state standards.</t>
         </is>
       </c>
       <c r="D2" s="8" t="n">
@@ -669,7 +669,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Taxpayers</t>
+          <t>State Legislature</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
@@ -679,47 +679,47 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Taxpayers directly fund school districts through local property tax levies, which supplement state aid and create funding disparities based on local wealth.</t>
+          <t>Legislature provides state aid to school districts through TEEOSA formula, which equalizes funding based on property valuations and student needs. Formula includes basic allowance, special education weighting, poverty adjustments, and transportation costs.</t>
         </is>
       </c>
       <c r="D3" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Taxpayers</t>
+          <t>Department of Education</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>State Legislature</t>
+          <t>School Districts</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Taxpayers provide property tax revenue that funds both state aid (via general fund) and local school district budgets. Nebraska relies heavily on property taxes for education funding, creating ongoing tension over tax equity.</t>
+          <t>Department of Education establishes academic standards and reporting requirements for school districts, including student performance benchmarks, teacher certification standards, and financial accountability measures.</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>School Districts</t>
+          <t>Taxpayers</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>State Legislature</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>School districts provide K-12 educational services to students, including classroom instruction, special education, extracurricular activities, transportation, food services, and counseling.</t>
+          <t>Taxpayers provide property tax revenue that funds both state aid (via general fund) and local school district budgets. Nebraska relies heavily on property taxes for education funding, creating ongoing tension over tax equity.</t>
         </is>
       </c>
       <c r="D5" s="8" t="n">
@@ -729,41 +729,41 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>State Legislature</t>
+          <t>Taxpayers</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Department of Education</t>
+          <t>School Districts</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Legislature grants Department of Education oversight authority over school districts, including power to audit financial records, review academic programs, and enforce state standards.</t>
+          <t>Taxpayers directly fund school districts through local property tax levies, which supplement state aid and create funding disparities based on local wealth.</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>State Legislature</t>
+          <t>School Districts</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>School Districts</t>
+          <t>Students</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Legislature provides state aid to school districts through TEEOSA formula, which equalizes funding based on property valuations and student needs. Formula includes basic allowance, special education weighting, poverty adjustments, and transportation costs.</t>
+          <t>School districts provide K-12 educational services to students, including classroom instruction, special education, extracurricular activities, transportation, food services, and counseling.</t>
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -841,31 +841,27 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
+          <t>State Legislature</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>School Districts</t>
-        </is>
-      </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>information</t>
+          <t>authority</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Academic performance standards, curriculum frameworks, assessment requirements, and data reporting specifications</t>
+          <t>Statutory authority to oversee school district compliance, conduct audits, and enforce academic standards</t>
         </is>
       </c>
       <c r="E2" s="9" t="n"/>
       <c r="F2" s="7" t="n"/>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>continuous</t>
-        </is>
-      </c>
+      <c r="G2" s="7" t="n"/>
       <c r="H2" s="9" t="n"/>
       <c r="I2" s="9" t="n">
         <v>1</v>
@@ -874,40 +870,46 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
+          <t>State Legislature</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>School Districts</t>
-        </is>
-      </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>authority</t>
+          <t>money</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Authority to conduct compliance audits, review instructional programs, and approve/deny accreditation</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="n"/>
-      <c r="F3" s="7" t="n"/>
+          <t>Department of Education operational budget for administration and oversight</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>USD/year</t>
+        </is>
+      </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>event-triggered</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="H3" s="9" t="n"/>
       <c r="I3" s="9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Taxpayers</t>
+          <t>State Legislature</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -922,7 +924,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Direct property tax levies for local school district operations</t>
+          <t>$800 million annual state aid appropriation distributed via TEEOSA formula</t>
         </is>
       </c>
       <c r="E4" s="9" t="n">
@@ -946,63 +948,51 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Taxpayers</t>
+          <t>State Legislature</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>State Legislature</t>
+          <t>School Districts</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>money</t>
+          <t>rule</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Property tax revenue collected at local and state levels to fund education</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>1200000000</v>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>USD/year</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>1500000000</v>
-      </c>
+          <t>TEEOSA formula compliance requirements including cost grouping, needs calculations, and local effort rate provisions</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="9" t="n"/>
       <c r="I5" s="9" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
+          <t>Department of Education</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
           <t>School Districts</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Students</t>
-        </is>
-      </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>information</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>K-12 instructional services including core subjects, special education, extracurricular activities, counseling, and transportation</t>
+          <t>Academic performance standards, curriculum frameworks, assessment requirements, and data reporting specifications</t>
         </is>
       </c>
       <c r="E6" s="9" t="n"/>
@@ -1014,18 +1004,18 @@
       </c>
       <c r="H6" s="9" t="n"/>
       <c r="I6" s="9" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>State Legislature</t>
+          <t>Department of Education</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Department of Education</t>
+          <t>School Districts</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -1035,12 +1025,16 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Statutory authority to oversee school district compliance, conduct audits, and enforce academic standards</t>
+          <t>Authority to conduct compliance audits, review instructional programs, and approve/deny accreditation</t>
         </is>
       </c>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>event-triggered</t>
+        </is>
+      </c>
       <c r="H7" s="9" t="n"/>
       <c r="I7" s="9" t="n">
         <v>1</v>
@@ -1049,14 +1043,14 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
+          <t>Taxpayers</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
           <t>State Legislature</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Department of Education</t>
-        </is>
-      </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
           <t>money</t>
@@ -1064,11 +1058,11 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Department of Education operational budget for administration and oversight</t>
+          <t>Property tax revenue collected at local and state levels to fund education</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>25000000</v>
+        <v>1200000000</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
@@ -1080,15 +1074,17 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="H8" s="9" t="n"/>
+      <c r="H8" s="9" t="n">
+        <v>1500000000</v>
+      </c>
       <c r="I8" s="9" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>State Legislature</t>
+          <t>Taxpayers</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -1103,7 +1099,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>$800 million annual state aid appropriation distributed via TEEOSA formula</t>
+          <t>Direct property tax levies for local school district operations</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
@@ -1127,30 +1123,34 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>State Legislature</t>
+          <t>School Districts</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>School Districts</t>
+          <t>Students</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>TEEOSA formula compliance requirements including cost grouping, needs calculations, and local effort rate provisions</t>
+          <t>K-12 instructional services including core subjects, special education, extracurricular activities, counseling, and transportation</t>
         </is>
       </c>
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="H10" s="9" t="n"/>
       <c r="I10" s="9" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
     </row>
   </sheetData>

--- a/examples/hayden_case_studies/nebraska_k12_finance.xlsx
+++ b/examples/hayden_case_studies/nebraska_k12_finance.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -49,6 +49,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -82,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,6 +103,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -530,7 +539,7 @@
 money: Department of Education operational budget for administratio...</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>money: $800 million annual state aid appropriation distributed via ...
 rule: TEEOSA formula compliance requirements including cost groupi...</t>
@@ -547,7 +556,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr"/>
       <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>information: Academic performance standards, curriculum frameworks, asses...
 authority: Authority to conduct compliance audits, review instructional...</t>
@@ -566,7 +575,7 @@
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>energy: K-12 instructional services including core subjects, special...</t>
         </is>
@@ -625,34 +634,34 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Delivery Count</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>State Legislature</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
@@ -662,17 +671,17 @@
           <t>Legislature grants Department of Education oversight authority over school districts, including power to audit financial records, review academic programs, and enforce state standards.</t>
         </is>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="9" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>State Legislature</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>School Districts</t>
         </is>
@@ -682,17 +691,17 @@
           <t>Legislature provides state aid to school districts through TEEOSA formula, which equalizes funding based on property valuations and student needs. Formula includes basic allowance, special education weighting, poverty adjustments, and transportation costs.</t>
         </is>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="9" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>School Districts</t>
         </is>
@@ -702,17 +711,17 @@
           <t>Department of Education establishes academic standards and reporting requirements for school districts, including student performance benchmarks, teacher certification standards, and financial accountability measures.</t>
         </is>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="9" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Taxpayers</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>State Legislature</t>
         </is>
@@ -722,17 +731,17 @@
           <t>Taxpayers provide property tax revenue that funds both state aid (via general fund) and local school district budgets. Nebraska relies heavily on property taxes for education funding, creating ongoing tension over tax equity.</t>
         </is>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="9" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Taxpayers</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>School Districts</t>
         </is>
@@ -742,17 +751,17 @@
           <t>Taxpayers directly fund school districts through local property tax levies, which supplement state aid and create funding disparities based on local wealth.</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="9" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>School Districts</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Students</t>
         </is>
@@ -762,7 +771,7 @@
           <t>School districts provide K-12 educational services to students, including classroom instruction, special education, extracurricular activities, transportation, food services, and counseling.</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -839,17 +848,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>State Legislature</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>authority</t>
         </is>
@@ -859,26 +868,26 @@
           <t>Statutory authority to oversee school district compliance, conduct audits, and enforce academic standards</t>
         </is>
       </c>
-      <c r="E2" s="9" t="n"/>
-      <c r="F2" s="7" t="n"/>
-      <c r="G2" s="7" t="n"/>
-      <c r="H2" s="9" t="n"/>
-      <c r="I2" s="9" t="n">
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>State Legislature</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>money</t>
         </is>
@@ -888,36 +897,36 @@
           <t>Department of Education operational budget for administration and oversight</t>
         </is>
       </c>
-      <c r="E3" s="9" t="n">
+      <c r="E3" s="10" t="n">
         <v>25000000</v>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>USD/year</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
-      <c r="H3" s="9" t="n"/>
-      <c r="I3" s="9" t="n">
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="10" t="n">
         <v>0.9</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>State Legislature</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>School Districts</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>money</t>
         </is>
@@ -927,36 +936,36 @@
           <t>$800 million annual state aid appropriation distributed via TEEOSA formula</t>
         </is>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="10" t="n">
         <v>800000000</v>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>USD/year</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
-      <c r="H4" s="9" t="n"/>
-      <c r="I4" s="9" t="n">
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="10" t="n">
         <v>0.95</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>State Legislature</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>School Districts</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>rule</t>
         </is>
@@ -966,26 +975,26 @@
           <t>TEEOSA formula compliance requirements including cost grouping, needs calculations, and local effort rate provisions</t>
         </is>
       </c>
-      <c r="E5" s="9" t="n"/>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="9" t="n"/>
-      <c r="I5" s="9" t="n">
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>School Districts</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>information</t>
         </is>
@@ -995,30 +1004,30 @@
           <t>Academic performance standards, curriculum frameworks, assessment requirements, and data reporting specifications</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="H6" s="9" t="n"/>
-      <c r="I6" s="9" t="n">
+      <c r="H6" s="10" t="n"/>
+      <c r="I6" s="10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>School Districts</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>authority</t>
         </is>
@@ -1028,30 +1037,30 @@
           <t>Authority to conduct compliance audits, review instructional programs, and approve/deny accreditation</t>
         </is>
       </c>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>event-triggered</t>
         </is>
       </c>
-      <c r="H7" s="9" t="n"/>
-      <c r="I7" s="9" t="n">
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Taxpayers</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>State Legislature</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>money</t>
         </is>
@@ -1061,38 +1070,38 @@
           <t>Property tax revenue collected at local and state levels to fund education</t>
         </is>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="10" t="n">
         <v>1200000000</v>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>USD/year</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
-      <c r="H8" s="9" t="n">
+      <c r="H8" s="10" t="n">
         <v>1500000000</v>
       </c>
-      <c r="I8" s="9" t="n">
+      <c r="I8" s="10" t="n">
         <v>0.92</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Taxpayers</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>School Districts</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>money</t>
         </is>
@@ -1102,36 +1111,36 @@
           <t>Direct property tax levies for local school district operations</t>
         </is>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="10" t="n">
         <v>800000000</v>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>USD/year</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
-      <c r="H9" s="9" t="n"/>
-      <c r="I9" s="9" t="n">
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="10" t="n">
         <v>0.95</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>School Districts</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Students</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>energy</t>
         </is>
@@ -1141,15 +1150,15 @@
           <t>K-12 instructional services including core subjects, special education, extracurricular activities, counseling, and transportation</t>
         </is>
       </c>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="H10" s="9" t="n"/>
-      <c r="I10" s="9" t="n">
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="10" t="n">
         <v>0.98</v>
       </c>
     </row>

--- a/examples/hayden_case_studies/nebraska_k12_finance.xlsx
+++ b/examples/hayden_case_studies/nebraska_k12_finance.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -47,8 +47,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -67,6 +67,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
         <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -106,6 +112,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -483,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -492,6 +501,11 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -525,6 +539,31 @@
           <t>Students</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Federal Department of Education</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>State Board of Education</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Local Communities</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Nebraska State Education Association (NSEA)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>County Property Assessors</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
@@ -547,6 +586,16 @@
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>authority: Governor appointment power (with legislative confirmation) f...
+money: State Board operational budget</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
@@ -564,6 +613,15 @@
       </c>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>information: ESSA compliance reports, test score data, accountability met...</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
@@ -580,6 +638,15 @@
           <t>energy: K-12 instructional services including core subjects, special...</t>
         </is>
       </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>information: School quality signals affecting property values (feedback t...</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
@@ -587,19 +654,24 @@
           <t>Taxpayers</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>money: Property tax revenue collected at local and state levels to ...</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>money: Direct property tax levies for local school district operati...</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
@@ -612,6 +684,126 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>information: Student achievement outcomes, graduation rates, college enro...</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Federal Department of Education</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>money: Title I grants, special education funding (IDEA), and other ...
+rule: ESSA compliance requirements, civil rights mandates, data re...</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>State Board of Education</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>rule: Academic content standards, teacher certification requiremen...</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Local Communities</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>authority: Electoral accountability via school board elections and budg...
+information: Demands for academic excellence, fiscal restraint, and local...</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Nebraska State Education Association (NSEA)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>information: Lobbying for local control, professional autonomy, and resis...</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>rule: Collective bargaining agreements on wages, working condition...</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>County Property Assessors</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>information: County property valuation data that drives TEEOSA formula ca...</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -624,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -634,144 +826,344 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Delivery Count</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>State Legislature</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>State Board of Education</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Legislature confirms State Board appointments and funds Board operations, creating hierarchical control despite Board's statutory independence.</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>State Legislature</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>School Districts</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Legislature provides state aid to school districts through TEEOSA formula, which equalizes funding based on property valuations and student needs. Formula includes basic allowance, special education weighting, poverty adjustments, and transportation costs.</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>State Legislature</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Legislature grants Department of Education oversight authority over school districts, including power to audit financial records, review academic programs, and enforce state standards.</t>
         </is>
       </c>
-      <c r="D2" s="9" t="n">
+      <c r="D4" s="10" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Federal Department of Education</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Department of Education</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Federal Department of Education provides categorical grants to Nebraska for Title I (low-income schools), IDEA (special education), and other programs.</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>State Board of Education</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Department of Education</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>State Board of Education sets academic standards that Department must enforce. Board is appointed by governor but operates with statutory independence.</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Local Communities</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Student outcomes create feedback loop: performance data drives community demands for district accountability, completing circular causation path.</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Taxpayers</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>State Legislature</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Taxpayers provide property tax revenue that funds both state aid (via general fund) and local school district budgets. Nebraska relies heavily on property taxes for education funding, creating ongoing tension over tax equity.</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Taxpayers</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>School Districts</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Legislature provides state aid to school districts through TEEOSA formula, which equalizes funding based on property valuations and student needs. Formula includes basic allowance, special education weighting, poverty adjustments, and transportation costs.</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="n">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Taxpayers directly fund school districts through local property tax levies, which supplement state aid and create funding disparities based on local wealth.</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Nebraska State Education Association (NSEA)</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>State Legislature</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Nebraska State Education Association advocates for local control and teacher professional autonomy, creating ceremonial resistance to state accountability mandates. Demonstrates Veblen-Hayden ceremonial vs instrumental conflict.</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Nebraska State Education Association (NSEA)</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>School Districts</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Teachers union negotiates contracts that constrain district flexibility, creating tension between formula efficiency and labor agreements.</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Local Communities</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>School Districts</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Local communities exercise democratic control over school districts through elected school boards and budget referendums, creating ceremonial preference for local autonomy over state-mandated equalization.</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>School Districts</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>School districts provide K-12 educational services to students, including classroom instruction, special education, extracurricular activities, transportation, food services, and counseling.</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>School Districts</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>County Property Assessors</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>School district performance affects local property values, which assessors capture in valuations. Creates circular causation: better schools → higher property values → higher local resources → different TEEOSA needs calculation.</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Federal Department of Education</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Nebraska reports to federal government on ESSA compliance, creating hierarchical accountability chain: federal → state → districts.</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Department of Education</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>School Districts</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Department of Education establishes academic standards and reporting requirements for school districts, including student performance benchmarks, teacher certification standards, and financial accountability measures.</t>
         </is>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D16" s="10" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Taxpayers</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>County Property Assessors</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>State Legislature</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Taxpayers provide property tax revenue that funds both state aid (via general fund) and local school district budgets. Nebraska relies heavily on property taxes for education funding, creating ongoing tension over tax equity.</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Taxpayers</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>School Districts</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Taxpayers directly fund school districts through local property tax levies, which supplement state aid and create funding disparities based on local wealth.</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>School Districts</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>School districts provide K-12 educational services to students, including classroom instruction, special education, extracurricular activities, transportation, food services, and counseling.</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="n">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>County assessors provide property valuation data that Legislature uses in TEEOSA formula. Valuations determine each district's 'needs' and 'resources', creating circular causation with funding allocations.</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -786,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -848,318 +1240,747 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>State Legislature</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>State Board of Education</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>authority</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Governor appointment power (with legislative confirmation) for Board members</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="9" t="n"/>
+      <c r="G2" s="9" t="n"/>
+      <c r="H2" s="11" t="n"/>
+      <c r="I2" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>State Legislature</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>State Board of Education</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>money</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>State Board operational budget</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>USD/year</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="11" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>State Legislature</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>School Districts</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>money</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>$800 million annual state aid appropriation distributed via TEEOSA formula</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>800000000</v>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>USD/year</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="n"/>
+      <c r="I4" s="11" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>State Legislature</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>School Districts</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>TEEOSA formula compliance requirements including cost grouping, needs calculations, and local effort rate provisions</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="11" t="n"/>
+      <c r="I5" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>State Legislature</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>authority</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Statutory authority to oversee school district compliance, conduct audits, and enforce academic standards</t>
         </is>
       </c>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="8" t="n"/>
-      <c r="G2" s="8" t="n"/>
-      <c r="H2" s="10" t="n"/>
-      <c r="I2" s="10" t="n">
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="11" t="n"/>
+      <c r="I6" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>State Legislature</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>money</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Department of Education operational budget for administration and oversight</t>
         </is>
       </c>
-      <c r="E3" s="10" t="n">
+      <c r="E7" s="11" t="n">
         <v>25000000</v>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>USD/year</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
-      <c r="H3" s="10" t="n"/>
-      <c r="I3" s="10" t="n">
+      <c r="H7" s="11" t="n"/>
+      <c r="I7" s="11" t="n">
         <v>0.9</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Federal Department of Education</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Department of Education</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>money</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Title I grants, special education funding (IDEA), and other federal programs</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>USD/year</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="n"/>
+      <c r="I8" s="11" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Federal Department of Education</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Department of Education</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>ESSA compliance requirements, civil rights mandates, data reporting standards</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="n"/>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="11" t="n"/>
+      <c r="I9" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>State Board of Education</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Department of Education</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Academic content standards, teacher certification requirements, graduation criteria</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="11" t="n"/>
+      <c r="I10" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Local Communities</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>information</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Student achievement outcomes, graduation rates, college enrollment data</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="n"/>
+      <c r="I11" s="11" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Taxpayers</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>State Legislature</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>money</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Property tax revenue collected at local and state levels to fund education</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>1200000000</v>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>USD/year</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="n">
+        <v>1500000000</v>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Taxpayers</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>School Districts</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>money</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>$800 million annual state aid appropriation distributed via TEEOSA formula</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="n">
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Direct property tax levies for local school district operations</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="n">
         <v>800000000</v>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>USD/year</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
-      <c r="H4" s="10" t="n"/>
-      <c r="I4" s="10" t="n">
+      <c r="H13" s="11" t="n"/>
+      <c r="I13" s="11" t="n">
         <v>0.95</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Nebraska State Education Association (NSEA)</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>State Legislature</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>information</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Lobbying for local control, professional autonomy, and resistance to centralized accountability (ceremonial preservation of status quo)</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="n"/>
+      <c r="I14" s="11" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Nebraska State Education Association (NSEA)</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>School Districts</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>rule</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>TEEOSA formula compliance requirements including cost grouping, needs calculations, and local effort rate provisions</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
-      <c r="H5" s="10" t="n"/>
-      <c r="I5" s="10" t="n">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Collective bargaining agreements on wages, working conditions, class sizes</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>periodic</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="11" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Local Communities</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>School Districts</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>authority</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Electoral accountability via school board elections and budget approval votes</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>event-triggered</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="n"/>
+      <c r="I16" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Local Communities</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>School Districts</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>information</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Demands for academic excellence, fiscal restraint, and local responsiveness</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="n"/>
+      <c r="I17" s="11" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>School Districts</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>energy</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>K-12 instructional services including core subjects, special education, extracurricular activities, counseling, and transportation</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="n"/>
+      <c r="I18" s="11" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>School Districts</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>County Property Assessors</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>information</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>School quality signals affecting property values (feedback to assessment system)</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="n"/>
+      <c r="I19" s="11" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Federal Department of Education</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>information</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>ESSA compliance reports, test score data, accountability metrics</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="n"/>
+      <c r="I20" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Department of Education</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>School Districts</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>information</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Academic performance standards, curriculum frameworks, assessment requirements, and data reporting specifications</t>
         </is>
       </c>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="10" t="n">
+      <c r="H21" s="11" t="n"/>
+      <c r="I21" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>School Districts</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>authority</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Authority to conduct compliance audits, review instructional programs, and approve/deny accreditation</t>
         </is>
       </c>
-      <c r="E7" s="10" t="n"/>
-      <c r="F7" s="8" t="n"/>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="9" t="inlineStr">
         <is>
           <t>event-triggered</t>
         </is>
       </c>
-      <c r="H7" s="10" t="n"/>
-      <c r="I7" s="10" t="n">
+      <c r="H22" s="11" t="n"/>
+      <c r="I22" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Taxpayers</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>County Property Assessors</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>State Legislature</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Property tax revenue collected at local and state levels to fund education</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>1200000000</v>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>USD/year</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>information</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>County property valuation data that drives TEEOSA formula calculations</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
-      <c r="H8" s="10" t="n">
-        <v>1500000000</v>
-      </c>
-      <c r="I8" s="10" t="n">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Taxpayers</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>School Districts</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Direct property tax levies for local school district operations</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>800000000</v>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>USD/year</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="n"/>
-      <c r="I9" s="10" t="n">
+      <c r="H23" s="11" t="n"/>
+      <c r="I23" s="11" t="n">
         <v>0.95</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>School Districts</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>energy</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>K-12 instructional services including core subjects, special education, extracurricular activities, counseling, and transportation</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>continuous</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="n"/>
-      <c r="I10" s="10" t="n">
-        <v>0.98</v>
       </c>
     </row>
   </sheetData>
